--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F367"/>
+  <dimension ref="A1:F369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8116,44 +8116,44 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -8175,7 +8175,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8190,24 +8190,24 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8239,96 +8239,96 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8340,27 +8340,27 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1065</t>
         </is>
       </c>
     </row>
@@ -8372,27 +8372,27 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -8404,49 +8404,49 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>天安@1065</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -8456,29 +8456,29 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -8500,34 +8500,34 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -8542,56 +8542,56 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8606,24 +8606,24 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8655,7 +8655,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8670,39 +8670,39 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -8724,27 +8724,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8756,27 +8756,27 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1064</t>
         </is>
       </c>
     </row>
@@ -8788,17 +8788,17 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>天安@1064</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -8820,49 +8820,49 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -8884,27 +8884,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -8916,27 +8916,27 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -8948,59 +8948,59 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -9012,34 +9012,34 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9071,7 +9071,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9103,7 +9103,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9118,39 +9118,39 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9204,27 +9204,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9236,27 +9236,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9268,17 +9268,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9288,39 +9288,39 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -9332,27 +9332,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9364,27 +9364,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9396,34 +9396,34 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9438,39 +9438,39 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,29 +9480,29 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9524,27 +9524,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9556,27 +9556,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9588,27 +9588,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9620,17 +9620,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9640,39 +9640,39 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9748,113 +9748,113 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -9876,27 +9876,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9908,27 +9908,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9940,81 +9940,81 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10036,81 +10036,81 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -10120,29 +10120,29 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10164,27 +10164,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10196,81 +10196,81 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10292,17 +10292,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -10324,34 +10324,34 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10376,71 +10376,71 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10452,17 +10452,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -10484,27 +10484,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10516,49 +10516,49 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10568,29 +10568,29 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10612,123 +10612,123 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10740,17 +10740,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -10772,27 +10772,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -10804,49 +10804,49 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10856,29 +10856,29 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10900,27 +10900,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -10932,49 +10932,49 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10984,24 +10984,24 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -11028,49 +11028,49 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11087,17 +11087,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -11124,17 +11124,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11156,17 +11156,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11188,49 +11188,49 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,39 +11240,39 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11284,27 +11284,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11316,27 +11316,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11348,113 +11348,113 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>太阳城@415</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>太阳城@415</t>
         </is>
       </c>
     </row>
@@ -11476,17 +11476,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11508,17 +11508,17 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -11528,29 +11528,29 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11560,39 +11560,39 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -11604,91 +11604,91 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11700,17 +11700,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,29 +11720,29 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,39 +11752,39 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11796,91 +11796,91 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11892,17 +11892,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,14 +11912,14 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11934,24 +11934,24 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11966,81 +11966,81 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12052,49 +12052,49 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -12104,69 +12104,133 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
+      <c r="C369" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D369" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E367" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F369"/>
+  <dimension ref="A1:F371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8180,59 +8180,59 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8574,113 +8574,113 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8692,27 +8692,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1064</t>
         </is>
       </c>
     </row>
@@ -8724,27 +8724,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -8756,91 +8756,91 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>天安@1064</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -8852,17 +8852,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -8884,162 +8884,162 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9071,7 +9071,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9086,39 +9086,39 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9140,27 +9140,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9204,27 +9204,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9236,17 +9236,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -9256,39 +9256,39 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -9300,27 +9300,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9332,27 +9332,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9364,34 +9364,34 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9406,49 +9406,49 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10127,64 +10127,64 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10260,81 +10260,81 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10356,17 +10356,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -10388,34 +10388,34 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10430,7 +10430,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10440,71 +10440,71 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10516,17 +10516,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10580,49 +10580,49 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10632,29 +10632,29 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10676,123 +10676,123 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10804,17 +10804,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -10836,27 +10836,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -10868,49 +10868,49 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,29 +10920,29 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10964,27 +10964,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -10996,49 +10996,49 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11048,24 +11048,24 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -11092,49 +11092,49 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11151,17 +11151,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -11188,17 +11188,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11220,17 +11220,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11252,49 +11252,49 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11304,39 +11304,39 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11348,27 +11348,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11412,113 +11412,113 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>太阳城@415</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>太阳城@415</t>
         </is>
       </c>
     </row>
@@ -11540,17 +11540,17 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11572,17 +11572,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -11592,29 +11592,29 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -11624,39 +11624,39 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -11668,91 +11668,91 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11764,17 +11764,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -11784,29 +11784,29 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,39 +11816,39 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11860,91 +11860,91 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11956,17 +11956,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -11976,14 +11976,14 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11998,24 +11998,24 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12030,24 +12030,24 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12072,14 +12072,14 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -12094,24 +12094,24 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12136,14 +12136,14 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12175,62 +12175,126 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr">
+      <c r="C371" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
+      <c r="D371" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E369" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F371"/>
+  <dimension ref="A1:F372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8468,49 +8468,49 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -8520,125 +8520,125 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -8820,27 +8820,27 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -8852,59 +8852,59 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -8916,34 +8916,34 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8975,32 +8975,32 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -9012,34 +9012,34 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9054,39 +9054,39 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9140,27 +9140,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9204,17 +9204,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9224,39 +9224,39 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -9268,27 +9268,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9300,27 +9300,27 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9332,34 +9332,34 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9374,103 +9374,103 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,29 +9480,29 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9524,27 +9524,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9556,27 +9556,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9588,27 +9588,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
@@ -9620,17 +9620,17 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9640,39 +9640,39 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9748,34 +9748,34 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9790,39 +9790,39 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10164,17 +10164,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10184,39 +10184,39 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10292,27 +10292,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10324,17 +10324,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10344,39 +10344,39 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10388,27 +10388,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -10420,27 +10420,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10452,81 +10452,81 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -10580,27 +10580,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10612,17 +10612,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10632,7 +10632,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10644,59 +10644,59 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10708,27 +10708,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -10740,34 +10740,34 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10782,39 +10782,39 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10836,27 +10836,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -10868,27 +10868,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -10900,17 +10900,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10932,59 +10932,59 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10996,27 +10996,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -11028,27 +11028,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11060,59 +11060,59 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11124,27 +11124,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11156,17 +11156,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11176,29 +11176,29 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11220,17 +11220,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11252,17 +11252,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11284,17 +11284,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11316,59 +11316,59 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11380,17 +11380,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11476,17 +11476,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11496,46 +11496,46 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>太阳城@415</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>太阳城@415</t>
         </is>
       </c>
     </row>
@@ -11572,17 +11572,17 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11604,17 +11604,17 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11636,17 +11636,17 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,29 +11656,29 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -11700,27 +11700,27 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -11732,59 +11732,59 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11796,17 +11796,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11828,17 +11828,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11848,29 +11848,29 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11892,27 +11892,27 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>太阳城@416</t>
         </is>
       </c>
     </row>
@@ -11924,59 +11924,59 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
@@ -12020,17 +12020,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -12040,24 +12040,24 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -12084,27 +12084,27 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12116,59 +12116,59 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12180,66 +12180,66 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -12271,30 +12271,62 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
+      <c r="C372" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
+      <c r="D372" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E371" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F372"/>
+  <dimension ref="A1:F390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8532,155 +8532,155 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
@@ -8692,27 +8692,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>天安@1064</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -8724,27 +8724,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8756,81 +8756,81 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1064</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -8852,194 +8852,194 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1016</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9054,88 +9054,88 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9150,24 +9150,24 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9182,17 +9182,17 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9204,34 +9204,34 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9246,24 +9246,24 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9278,24 +9278,24 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9310,24 +9310,24 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9342,39 +9342,39 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9384,14 +9384,14 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9406,39 +9406,39 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9448,110 +9448,110 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -9566,103 +9566,103 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,189 +9672,189 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9864,61 +9864,61 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9928,78 +9928,78 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10014,88 +10014,88 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10110,56 +10110,56 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10184,29 +10184,29 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,93 +10216,93 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,29 +10312,29 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10344,78 +10344,78 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10430,88 +10430,88 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -10543,7 +10543,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -10558,24 +10558,24 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -10607,7 +10607,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10632,14 +10632,14 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10654,24 +10654,24 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10703,7 +10703,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10728,14 +10728,14 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -10767,7 +10767,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10782,103 +10782,103 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,29 +10888,29 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,24 +10920,24 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -10952,61 +10952,61 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -11016,93 +11016,93 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11112,78 +11112,78 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11198,66 +11198,66 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -11279,22 +11279,22 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11304,88 +11304,88 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -11400,125 +11400,125 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -11528,29 +11528,29 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11560,120 +11560,120 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>太阳城@415</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11688,29 +11688,29 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,93 +11720,93 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,29 +11816,29 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11848,61 +11848,61 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,157 +11912,157 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>太阳城@416</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12072,46 +12072,46 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12126,56 +12126,56 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -12200,61 +12200,61 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12264,14 +12264,14 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,37 +12296,613 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>国金@2108</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>袁芷澜</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>国金@2108</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>天安@1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>国金@2108</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C372" t="inlineStr">
+      <c r="C390" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D390" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E372" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -8227,7 +8227,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -8495,7 +8495,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8510,17 +8510,17 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -8532,66 +8532,66 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8606,17 +8606,17 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -8628,49 +8628,49 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -8692,27 +8692,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8724,27 +8724,27 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1064</t>
         </is>
       </c>
     </row>
@@ -8756,17 +8756,17 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>天安@1064</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -8788,49 +8788,49 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -8852,17 +8852,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -8884,59 +8884,59 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@1016</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@1016</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -8948,59 +8948,59 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9012,59 +9012,59 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -9076,59 +9076,59 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9140,49 +9140,49 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9204,27 +9204,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9236,27 +9236,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9268,27 +9268,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9300,17 +9300,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9320,39 +9320,39 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9364,27 +9364,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9396,27 +9396,27 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9428,49 +9428,49 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9492,66 +9492,66 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F390"/>
+  <dimension ref="A1:F389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8500,66 +8500,66 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -8596,49 +8596,49 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -8660,27 +8660,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8692,27 +8692,27 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1064</t>
         </is>
       </c>
     </row>
@@ -8724,17 +8724,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>天安@1064</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -8756,49 +8756,49 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -8820,17 +8820,17 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -8852,59 +8852,59 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@1016</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>天安@1016</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -8916,59 +8916,59 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -8980,59 +8980,59 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -9044,59 +9044,59 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9108,49 +9108,49 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9204,27 +9204,27 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9236,27 +9236,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9268,17 +9268,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9288,39 +9288,39 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9332,27 +9332,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9364,27 +9364,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9396,49 +9396,49 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9460,66 +9460,66 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -9556,59 +9556,59 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9620,49 +9620,49 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9748,27 +9748,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9800,39 +9800,39 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9844,27 +9844,27 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9876,27 +9876,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>国金@2105</t>
         </is>
       </c>
     </row>
@@ -9908,49 +9908,49 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9960,7 +9960,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9972,91 +9972,91 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10068,17 +10068,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,39 +10088,39 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10132,27 +10132,27 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10164,17 +10164,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10228,17 +10228,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10248,39 +10248,39 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10292,27 +10292,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10324,27 +10324,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10356,22 +10356,22 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -10383,39 +10383,39 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10447,32 +10447,32 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10484,17 +10484,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10504,39 +10504,39 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10580,27 +10580,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10612,27 +10612,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -10644,17 +10644,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10664,39 +10664,39 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10708,27 +10708,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10740,27 +10740,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10772,49 +10772,49 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10824,14 +10824,14 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10863,54 +10863,54 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -10932,27 +10932,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10964,27 +10964,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10996,17 +10996,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11028,59 +11028,59 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -11092,27 +11092,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11124,49 +11124,49 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11176,14 +11176,14 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11215,54 +11215,54 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11284,27 +11284,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -11316,27 +11316,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -11348,17 +11348,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11380,59 +11380,59 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11476,27 +11476,27 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11508,66 +11508,66 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11599,22 +11599,22 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11636,27 +11636,27 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11668,17 +11668,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -11688,29 +11688,29 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11732,17 +11732,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11764,17 +11764,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11796,17 +11796,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -11828,59 +11828,59 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11892,17 +11892,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11924,27 +11924,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11956,27 +11956,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11988,17 +11988,17 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12008,39 +12008,39 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12052,34 +12052,34 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -12111,32 +12111,32 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12148,17 +12148,17 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12180,17 +12180,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12212,17 +12212,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -12232,29 +12232,29 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -12276,27 +12276,27 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12308,59 +12308,59 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12372,17 +12372,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12404,17 +12404,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,29 +12424,29 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -12468,27 +12468,27 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12500,59 +12500,59 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,24 +12616,24 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -12660,27 +12660,27 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12692,59 +12692,59 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -12756,66 +12756,66 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -12847,7 +12847,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12871,38 +12871,6 @@
         </is>
       </c>
       <c r="F389" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C390" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E390" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -8564,49 +8564,49 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -8628,27 +8628,27 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -8660,27 +8660,27 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1064</t>
         </is>
       </c>
     </row>
@@ -8692,66 +8692,66 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>天安@1064</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -8766,56 +8766,56 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1016</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -8830,39 +8830,39 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8872,142 +8872,142 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>天安@1016</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2114</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9022,24 +9022,24 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9054,81 +9054,81 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9140,17 +9140,17 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9204,81 +9204,81 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9300,34 +9300,34 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9342,39 +9342,39 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -9384,46 +9384,46 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9438,24 +9438,24 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9487,39 +9487,39 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>国金@2118</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -9534,39 +9534,39 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9576,71 +9576,71 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9652,17 +9652,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
@@ -9716,81 +9716,81 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -9812,34 +9812,34 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -9854,39 +9854,39 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -9896,29 +9896,29 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>国金@2105</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9928,61 +9928,61 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9992,29 +9992,29 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10024,14 +10024,14 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10056,29 +10056,29 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10100,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10132,49 +10132,49 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10184,29 +10184,29 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,39 +10216,39 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10260,34 +10260,34 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10302,209 +10302,209 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10516,27 +10516,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -10580,81 +10580,81 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10676,17 +10676,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10708,81 +10708,81 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10792,93 +10792,93 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -10900,27 +10900,27 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10932,27 +10932,27 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10964,17 +10964,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10996,59 +10996,59 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -11060,27 +11060,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11092,49 +11092,49 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11144,14 +11144,14 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11183,32 +11183,32 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11348,59 +11348,59 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11444,27 +11444,27 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11476,66 +11476,66 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11567,22 +11567,22 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11604,27 +11604,27 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11636,17 +11636,17 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,29 +11656,29 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11700,17 +11700,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11732,17 +11732,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11764,17 +11764,17 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -11796,59 +11796,59 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11860,17 +11860,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11892,27 +11892,27 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11924,27 +11924,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11956,17 +11956,17 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -11976,39 +11976,39 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12020,34 +12020,34 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -12079,32 +12079,32 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F389"/>
+  <dimension ref="A1:F400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9903,7 +9903,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -9918,49 +9918,49 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9972,17 +9972,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9992,61 +9992,61 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10068,27 +10068,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10100,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10132,81 +10132,81 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10260,49 +10260,49 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,14 +10312,14 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10334,24 +10334,24 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10383,103 +10383,103 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10494,24 +10494,24 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -10526,24 +10526,24 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -10558,17 +10558,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10580,34 +10580,34 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10622,24 +10622,24 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10654,24 +10654,24 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10686,24 +10686,24 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -10718,56 +10718,56 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -10782,39 +10782,39 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10824,110 +10824,110 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10942,39 +10942,39 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10984,61 +10984,61 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11048,61 +11048,61 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11112,14 +11112,14 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11134,103 +11134,103 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,61 +11240,61 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11304,14 +11304,14 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -11326,167 +11326,167 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11496,61 +11496,61 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11560,93 +11560,93 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,93 +11656,93 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,253 +11752,253 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12008,14 +12008,14 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12030,88 +12030,88 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12143,7 +12143,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -12168,14 +12168,14 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -12190,24 +12190,24 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -12222,103 +12222,103 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -12328,46 +12328,46 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -12382,39 +12382,39 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,125 +12424,125 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12552,29 +12552,29 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,29 +12584,29 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,120 +12616,120 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -12744,14 +12744,14 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -12766,24 +12766,24 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -12808,69 +12808,421 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>天安@1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>国金@2108</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr">
+      <c r="C400" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
+      <c r="D400" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E389" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F400"/>
+  <dimension ref="A1:F405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8852,17 +8852,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -8884,59 +8884,59 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -8948,59 +8948,59 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>国金@2114</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -9012,27 +9012,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2114</t>
         </is>
       </c>
     </row>
@@ -9044,49 +9044,49 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9140,27 +9140,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9204,17 +9204,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9224,39 +9224,39 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -9268,27 +9268,27 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9396,34 +9396,34 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -9460,49 +9460,49 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>国金@2118</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
@@ -9524,27 +9524,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2118</t>
         </is>
       </c>
     </row>
@@ -9556,49 +9556,49 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9620,27 +9620,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9652,27 +9652,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9716,17 +9716,17 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -9736,39 +9736,39 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -9780,27 +9780,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9908,22 +9908,22 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -9935,7 +9935,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9950,49 +9950,49 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10004,27 +10004,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10036,59 +10036,59 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10100,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10164,27 +10164,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10196,17 +10196,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,39 +10216,39 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10292,27 +10292,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10324,22 +10324,22 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -10351,32 +10351,32 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10388,81 +10388,81 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10472,46 +10472,46 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -10526,17 +10526,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10548,17 +10548,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10568,29 +10568,29 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10600,39 +10600,39 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10644,27 +10644,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10676,27 +10676,27 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10708,81 +10708,81 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10804,17 +10804,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10836,98 +10836,98 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -10959,7 +10959,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -10974,24 +10974,24 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11023,49 +11023,49 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -11080,61 +11080,61 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11156,17 +11156,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11188,49 +11188,49 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,110 +11240,110 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -11358,39 +11358,39 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11400,142 +11400,142 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11550,24 +11550,24 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11582,71 +11582,71 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,78 +11656,78 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11742,56 +11742,56 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11806,39 +11806,39 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11848,221 +11848,221 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12072,46 +12072,46 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12143,7 +12143,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12168,14 +12168,14 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -12190,24 +12190,24 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -12222,24 +12222,24 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -12271,7 +12271,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,46 +12296,46 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -12350,39 +12350,39 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -12392,110 +12392,110 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -12510,24 +12510,24 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -12559,39 +12559,39 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,93 +12616,93 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12712,29 +12712,29 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12776,125 +12776,125 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -12968,120 +12968,120 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -13096,14 +13096,14 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,24 +13118,24 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -13160,69 +13160,229 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr">
+      <c r="C405" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr">
+      <c r="D405" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F405"/>
+  <dimension ref="A1:F407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9300,49 +9300,49 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1022</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -9364,49 +9364,49 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9416,167 +9416,167 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>国金@2118</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
@@ -9588,17 +9588,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9608,71 +9608,71 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2118</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9684,17 +9684,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9748,66 +9748,66 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9822,56 +9822,56 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9886,39 +9886,39 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9928,61 +9928,61 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9992,46 +9992,46 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10046,17 +10046,17 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10068,17 +10068,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,61 +10088,61 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10164,27 +10164,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10228,81 +10228,81 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10324,27 +10324,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10356,49 +10356,49 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10408,14 +10408,14 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10430,39 +10430,39 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10472,61 +10472,61 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -10536,46 +10536,46 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -10590,17 +10590,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10612,17 +10612,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -10632,29 +10632,29 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10664,39 +10664,39 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10708,27 +10708,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10740,27 +10740,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10772,81 +10772,81 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10868,17 +10868,17 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -10900,76 +10900,76 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10984,14 +10984,14 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11006,39 +11006,39 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11048,46 +11048,46 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11102,17 +11102,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11124,17 +11124,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11144,71 +11144,71 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11220,17 +11220,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11252,27 +11252,27 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11284,49 +11284,49 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -11336,29 +11336,29 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11380,34 +11380,34 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -11422,34 +11422,34 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11464,14 +11464,14 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -11486,39 +11486,39 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -11528,46 +11528,46 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11582,17 +11582,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11604,17 +11604,17 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -11624,71 +11624,71 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11700,17 +11700,17 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11732,49 +11732,49 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -11784,29 +11784,29 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11828,27 +11828,27 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -11860,49 +11860,49 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,46 +11912,46 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11966,39 +11966,39 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12008,71 +12008,71 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12084,49 +12084,49 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -12143,17 +12143,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -12180,17 +12180,17 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12212,17 +12212,17 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12244,49 +12244,49 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,39 +12296,39 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12340,27 +12340,27 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12372,27 +12372,27 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12404,81 +12404,81 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12488,46 +12488,46 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -12542,39 +12542,39 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,78 +12584,78 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -12744,29 +12744,29 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12776,39 +12776,39 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -12820,91 +12820,91 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,29 +12936,29 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -12968,39 +12968,39 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13012,91 +13012,91 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13128,29 +13128,29 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -13160,39 +13160,39 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13204,66 +13204,66 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -13288,14 +13288,14 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13327,62 +13327,126 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
+      <c r="C407" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
+      <c r="D407" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F407"/>
+  <dimension ref="A1:F404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9844,17 +9844,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10324,17 +10324,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10868,17 +10868,17 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11380,17 +11380,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11796,59 +11796,59 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -12276,59 +12276,59 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12340,17 +12340,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12372,27 +12372,27 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12404,27 +12404,27 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12436,17 +12436,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,39 +12456,39 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12500,49 +12500,49 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12564,34 +12564,34 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -12606,66 +12606,66 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12724,17 +12724,17 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12776,39 +12776,39 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12820,91 +12820,91 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12916,17 +12916,17 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,14 +12936,14 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12958,24 +12958,24 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12990,24 +12990,24 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13032,14 +13032,14 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -13054,24 +13054,24 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -13086,24 +13086,24 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13128,14 +13128,14 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13150,24 +13150,24 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -13182,24 +13182,24 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -13224,78 +13224,78 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13327,126 +13327,30 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
-        <is>
-          <t>天安@1032</t>
-        </is>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E405" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F405" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F404"/>
+  <dimension ref="A1:F409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9300,17 +9300,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@1022</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9332,81 +9332,81 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1022</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1123</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -9428,49 +9428,49 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,167 +9480,167 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>国金@2118</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
@@ -9652,17 +9652,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,71 +9672,71 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2118</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9748,17 +9748,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9780,27 +9780,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9812,66 +9812,66 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -9886,71 +9886,71 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -9960,24 +9960,24 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -9992,14 +9992,14 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10014,56 +10014,56 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -10078,24 +10078,24 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10120,125 +10120,125 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10292,49 +10292,49 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10344,29 +10344,29 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10376,39 +10376,39 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10420,34 +10420,34 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10462,88 +10462,88 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -10558,56 +10558,56 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10622,24 +10622,24 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10671,118 +10671,118 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10804,27 +10804,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10836,49 +10836,49 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,29 +10888,29 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,39 +10920,39 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10964,34 +10964,34 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11006,88 +11006,88 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11119,7 +11119,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11134,24 +11134,24 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11183,49 +11183,49 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -11240,61 +11240,61 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11316,17 +11316,17 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11348,49 +11348,49 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11400,110 +11400,110 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -11518,24 +11518,24 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11550,39 +11550,39 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -11592,142 +11592,142 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11742,24 +11742,24 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11774,24 +11774,24 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11828,98 +11828,98 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11934,56 +11934,56 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11998,24 +11998,24 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12030,39 +12030,39 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12072,253 +12072,253 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -12328,29 +12328,29 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,78 +12360,78 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -12463,7 +12463,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12488,125 +12488,125 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,29 +12616,29 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12648,46 +12648,46 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -12702,24 +12702,24 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -12734,12 +12734,12 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -12751,103 +12751,103 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -12872,14 +12872,14 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,14 +12936,14 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12975,7 +12975,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -13007,7 +13007,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13032,14 +13032,14 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -13071,7 +13071,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -13103,113 +13103,113 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13246,24 +13246,24 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -13288,69 +13288,229 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr">
+      <c r="C409" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr">
+      <c r="D409" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E404" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F409"/>
+  <dimension ref="A1:F414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8788,59 +8788,59 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -8852,17 +8852,17 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -8884,59 +8884,59 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -8948,59 +8948,59 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>程子萌</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2114</t>
         </is>
       </c>
     </row>
@@ -9012,27 +9012,27 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>国金@2114</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9044,49 +9044,49 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9140,27 +9140,27 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9172,27 +9172,27 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9204,17 +9204,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -9224,39 +9224,39 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9268,17 +9268,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>临时教学区 江宁银城校区VIP519教室</t>
         </is>
       </c>
     </row>
@@ -9300,17 +9300,17 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1022</t>
         </is>
       </c>
     </row>
@@ -9332,81 +9332,81 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@1022</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>天安@1123</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9428,49 +9428,49 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,167 +9480,167 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>国金@2118</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9652,17 +9652,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,71 +9672,71 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>国金@2118</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9748,17 +9748,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9780,27 +9780,27 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
@@ -9812,91 +9812,91 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9908,34 +9908,34 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -9950,24 +9950,24 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -9982,39 +9982,39 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10024,61 +10024,61 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,46 +10088,46 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -10142,17 +10142,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10164,17 +10164,17 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -10184,61 +10184,61 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10292,27 +10292,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10324,91 +10324,91 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10420,27 +10420,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10452,27 +10452,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10484,22 +10484,22 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -10511,32 +10511,32 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10996,27 +10996,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11028,27 +11028,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11060,49 +11060,49 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -11112,14 +11112,14 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11134,24 +11134,24 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11166,39 +11166,39 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -11208,46 +11208,46 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11262,17 +11262,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11284,17 +11284,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -11304,71 +11304,71 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11380,17 +11380,17 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11444,49 +11444,49 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11496,39 +11496,39 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11540,27 +11540,27 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11572,34 +11572,34 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -11614,34 +11614,34 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -11656,46 +11656,46 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -11727,7 +11727,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11742,24 +11742,24 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11791,49 +11791,49 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11848,61 +11848,61 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11924,81 +11924,81 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12008,29 +12008,29 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -12052,27 +12052,27 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12084,17 +12084,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -12104,14 +12104,14 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12126,34 +12126,34 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -12175,86 +12175,86 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12264,14 +12264,14 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -12286,24 +12286,24 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -12318,103 +12318,103 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,46 +12424,46 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -12495,7 +12495,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -12520,14 +12520,14 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -12542,24 +12542,24 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -12574,24 +12574,24 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -12623,7 +12623,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12648,125 +12648,125 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12776,29 +12776,29 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -12808,46 +12808,46 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12862,24 +12862,24 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -12911,103 +12911,103 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13032,14 +13032,14 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13064,14 +13064,14 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,14 +13096,14 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13135,7 +13135,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13167,7 +13167,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -13192,14 +13192,14 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -13231,7 +13231,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13263,113 +13263,113 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -13384,14 +13384,14 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -13406,24 +13406,24 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -13448,69 +13448,229 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C409" t="inlineStr">
+      <c r="C414" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
+      <c r="D414" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F414"/>
+  <dimension ref="A1:F420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9268,17 +9268,17 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>袁芷澜</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>临时教学区 江宁银城校区VIP519教室</t>
+          <t>天安@1022</t>
         </is>
       </c>
     </row>
@@ -9300,59 +9300,59 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@1022</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9364,27 +9364,27 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9396,59 +9396,59 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -9460,34 +9460,34 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -9524,49 +9524,49 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>国金@2118</t>
         </is>
       </c>
     </row>
@@ -9588,27 +9588,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>国金@2118</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9620,49 +9620,49 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9716,27 +9716,27 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9748,27 +9748,27 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9800,39 +9800,39 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9844,12 +9844,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -9876,49 +9876,49 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9940,59 +9940,59 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -10004,22 +10004,22 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -10031,7 +10031,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10046,49 +10046,49 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10100,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10132,59 +10132,59 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10228,17 +10228,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10292,17 +10292,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,39 +10312,39 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -10388,27 +10388,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -10420,27 +10420,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10452,22 +10452,22 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -10479,32 +10479,32 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -10516,27 +10516,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10548,59 +10548,59 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -10612,34 +10612,34 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10654,49 +10654,49 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10708,27 +10708,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10740,59 +10740,59 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10804,27 +10804,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10836,27 +10836,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10868,27 +10868,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -10900,17 +10900,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,39 +10920,39 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10996,27 +10996,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11028,27 +11028,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -11060,59 +11060,59 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -11124,27 +11124,27 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11156,27 +11156,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -12020,59 +12020,59 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -12116,27 +12116,27 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12148,27 +12148,27 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12180,49 +12180,49 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12244,49 +12244,49 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,61 +12296,61 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,71 +12360,71 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12436,49 +12436,49 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12495,17 +12495,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -12532,17 +12532,17 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12596,49 +12596,49 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12648,39 +12648,39 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12692,27 +12692,27 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12724,27 +12724,27 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12756,81 +12756,81 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -12840,46 +12840,46 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12894,39 +12894,39 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,78 +12936,78 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13022,7 +13022,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,14 +13096,14 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,24 +13118,24 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13150,24 +13150,24 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -13192,14 +13192,14 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -13214,24 +13214,24 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13246,103 +13246,103 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13352,29 +13352,29 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13384,152 +13384,152 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -13544,14 +13544,14 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13566,24 +13566,24 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,69 +13608,261 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>翟沅琪</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>天安@1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C414" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
+      <c r="D420" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -9000,71 +9000,71 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>国金@2114</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9076,17 +9076,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -9108,27 +9108,27 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -9140,91 +9140,91 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1022</t>
         </is>
       </c>
     </row>
@@ -9236,27 +9236,27 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@909</t>
         </is>
       </c>
     </row>
@@ -9268,59 +9268,59 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>天安@1022</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9332,27 +9332,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9364,59 +9364,59 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -9428,34 +9428,34 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -9492,49 +9492,49 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -9556,17 +9556,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9576,71 +9576,71 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>国金@2118</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9652,17 +9652,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
@@ -9716,91 +9716,91 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9812,12 +9812,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -9844,59 +9844,59 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10408,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10548,17 +10548,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -10568,39 +10568,39 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -10612,34 +10612,34 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10654,17 +10654,17 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11156,27 +11156,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -11247,32 +11247,32 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -11284,27 +11284,27 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11316,49 +11316,49 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11444,17 +11444,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11476,59 +11476,59 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11540,12 +11540,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -11572,27 +11572,27 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11604,27 +11604,27 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11636,17 +11636,17 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -11727,32 +11727,32 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11764,34 +11764,34 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11806,49 +11806,49 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11860,27 +11860,27 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11892,49 +11892,49 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11956,27 +11956,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11988,27 +11988,27 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -12020,17 +12020,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -12308,27 +12308,27 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
@@ -12884,49 +12884,49 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12948,34 +12948,34 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -12990,66 +12990,66 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -13160,29 +13160,29 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -13204,17 +13204,17 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13236,66 +13236,66 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13310,167 +13310,167 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13480,71 +13480,71 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13556,17 +13556,17 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13576,29 +13576,29 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,39 +13608,39 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13652,59 +13652,59 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>翟沅琪</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F420"/>
+  <dimension ref="A1:F421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1127</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9310,17 +9310,17 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>史心怡</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1125</t>
         </is>
       </c>
     </row>
@@ -9332,27 +9332,27 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9364,59 +9364,59 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
@@ -9428,34 +9428,34 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -9492,49 +9492,49 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
@@ -9556,17 +9556,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9576,71 +9576,71 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>史心怡</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9652,17 +9652,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9716,91 +9716,91 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1051</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -9812,27 +9812,27 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -9844,81 +9844,81 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -9940,49 +9940,49 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9992,61 +9992,61 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10056,46 +10056,46 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,61 +10152,61 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10292,91 +10292,91 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10388,27 +10388,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10420,27 +10420,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10452,91 +10452,91 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10580,17 +10580,17 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -10600,39 +10600,39 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -10644,59 +10644,59 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10708,27 +10708,27 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10740,59 +10740,59 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10804,27 +10804,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10836,27 +10836,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10868,27 +10868,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10900,17 +10900,17 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -10920,39 +10920,39 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10964,12 +10964,12 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -10996,27 +10996,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11028,27 +11028,27 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11060,59 +11060,59 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11668,27 +11668,27 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11700,59 +11700,59 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -11764,34 +11764,34 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -11806,49 +11806,49 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11860,27 +11860,27 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11892,49 +11892,49 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11956,27 +11956,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -11988,27 +11988,27 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -12020,59 +12020,59 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12084,12 +12084,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -12116,27 +12116,27 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12148,27 +12148,27 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12180,59 +12180,59 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12244,49 +12244,49 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,61 +12296,61 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,71 +12360,71 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12436,49 +12436,49 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12495,17 +12495,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -12532,17 +12532,17 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12564,17 +12564,17 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12596,49 +12596,49 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12648,39 +12648,39 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12692,27 +12692,27 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12724,27 +12724,27 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12756,91 +12756,91 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12852,27 +12852,27 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12884,27 +12884,27 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -12916,27 +12916,27 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -13492,27 +13492,27 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -13524,59 +13524,59 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13588,17 +13588,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
@@ -13620,17 +13620,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13640,24 +13640,24 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -13684,59 +13684,59 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13748,66 +13748,66 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -13839,30 +13839,62 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr">
+      <c r="C421" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
+      <c r="D421" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F421"/>
+  <dimension ref="A1:F418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9364,59 +9364,59 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -9428,34 +9428,34 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -9492,49 +9492,49 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -9556,27 +9556,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>史心怡</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -9588,49 +9588,49 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>史心怡</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9652,27 +9652,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9716,91 +9716,91 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1051</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9812,27 +9812,27 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9844,81 +9844,81 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9940,49 +9940,49 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9992,61 +9992,61 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10056,46 +10056,46 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,61 +10152,61 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10292,91 +10292,91 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10388,27 +10388,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10420,27 +10420,27 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10452,49 +10452,49 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10504,39 +10504,39 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10548,98 +10548,98 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10654,24 +10654,24 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -10708,17 +10708,17 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10728,29 +10728,29 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -10760,39 +10760,39 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10804,27 +10804,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10836,49 +10836,49 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,61 +10888,61 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -10964,17 +10964,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10996,34 +10996,34 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11038,24 +11038,24 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11070,34 +11070,34 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -11112,14 +11112,14 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11134,130 +11134,130 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -11272,61 +11272,61 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11348,17 +11348,17 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11380,49 +11380,49 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -11432,29 +11432,29 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11464,29 +11464,29 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11508,27 +11508,27 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11540,34 +11540,34 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11582,24 +11582,24 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -11614,39 +11614,39 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,14 +11656,14 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -11678,56 +11678,56 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -11742,24 +11742,24 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -11791,49 +11791,49 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -11848,61 +11848,61 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -11924,81 +11924,81 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -12008,29 +12008,29 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -12040,7 +12040,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12052,27 +12052,27 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12084,17 +12084,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -12104,14 +12104,14 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12126,24 +12126,24 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12158,56 +12158,56 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -12222,71 +12222,71 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,46 +12296,46 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -12350,24 +12350,24 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -12382,24 +12382,24 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,14 +12424,14 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12468,17 +12468,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12500,49 +12500,49 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12552,29 +12552,29 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,39 +12584,39 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12628,27 +12628,27 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12660,113 +12660,113 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12788,17 +12788,17 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -12820,49 +12820,49 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -12872,78 +12872,78 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12958,103 +12958,103 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,14 +13096,14 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,24 +13118,24 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13150,24 +13150,24 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -13182,34 +13182,34 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -13231,7 +13231,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13256,78 +13256,78 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -13342,56 +13342,56 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13416,14 +13416,14 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -13438,24 +13438,24 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -13470,24 +13470,24 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13512,14 +13512,14 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -13534,24 +13534,24 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13566,24 +13566,24 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,61 +13608,61 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13672,78 +13672,78 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -13775,126 +13775,30 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
-        <is>
-          <t>天安@1032</t>
-        </is>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E419" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F418"/>
+  <dimension ref="A1:F413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9327,7 +9327,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9342,88 +9342,88 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9438,71 +9438,71 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>史心怡</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -9512,14 +9512,14 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -9534,24 +9534,24 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -9566,56 +9566,56 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>史心怡</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9630,24 +9630,24 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9662,24 +9662,24 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -9704,14 +9704,14 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9726,56 +9726,56 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -9790,24 +9790,24 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -9822,39 +9822,39 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -9864,221 +9864,221 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>周宏胤</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>仙林高科校区 仙林高科校区VIP806教室</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,78 +10088,78 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10174,24 +10174,24 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -10216,14 +10216,14 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10238,24 +10238,24 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10270,24 +10270,24 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10302,103 +10302,103 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -10408,24 +10408,24 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -10440,29 +10440,29 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10472,189 +10472,189 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -10664,61 +10664,61 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -10728,93 +10728,93 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -10824,14 +10824,14 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -10846,184 +10846,184 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11038,24 +11038,24 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11070,103 +11070,103 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11176,78 +11176,78 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11272,14 +11272,14 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -11294,24 +11294,24 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -11326,24 +11326,24 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -11358,24 +11358,24 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -11390,162 +11390,162 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -11560,157 +11560,157 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,29 +11720,29 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,61 +11752,61 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,29 +11816,29 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11848,78 +11848,78 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -11934,199 +11934,199 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -12136,88 +12136,88 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -12232,93 +12232,93 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -12328,29 +12328,29 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12372,49 +12372,49 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,29 +12424,29 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,61 +12456,61 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12532,49 +12532,49 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -12584,24 +12584,24 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -12623,22 +12623,22 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12648,39 +12648,39 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12712,14 +12712,14 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -12734,24 +12734,24 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -12766,39 +12766,39 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -12808,29 +12808,29 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -12840,14 +12840,14 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12862,24 +12862,24 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -12911,39 +12911,39 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12958,88 +12958,88 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -13054,66 +13054,66 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -13135,135 +13135,135 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
@@ -13288,61 +13288,61 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -13352,29 +13352,29 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13384,24 +13384,24 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -13416,46 +13416,46 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -13487,7 +13487,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -13502,7 +13502,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13512,61 +13512,61 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -13576,14 +13576,14 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,197 +13608,37 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
-        <is>
-          <t>天安@1028</t>
-        </is>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C414" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F414" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>16:10:00</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
-        <is>
-          <t>18:10:00</t>
-        </is>
-      </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>陈博扬</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>AP微积分</t>
-        </is>
-      </c>
-      <c r="F415" t="inlineStr">
-        <is>
-          <t>天安@1032</t>
-        </is>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>2026-06-06</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C416" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E416" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F416" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C417" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C418" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E418" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F413"/>
+  <dimension ref="A1:F422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9391,7 +9391,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9406,17 +9406,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>史心怡</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -9428,49 +9428,49 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>史心怡</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9492,27 +9492,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1026</t>
         </is>
       </c>
     </row>
@@ -9524,27 +9524,27 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9556,17 +9556,17 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9812,22 +9812,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -9844,44 +9844,44 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9896,39 +9896,39 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -9940,27 +9940,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -9972,59 +9972,59 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10036,27 +10036,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10068,17 +10068,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10100,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,39 +10152,39 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10196,12 +10196,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10292,22 +10292,22 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -10479,22 +10479,22 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
@@ -10516,27 +10516,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10548,59 +10548,59 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -10612,27 +10612,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10644,27 +10644,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10676,59 +10676,59 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -10772,27 +10772,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10804,27 +10804,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -10836,49 +10836,49 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -10900,59 +10900,59 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10964,66 +10964,66 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -11060,17 +11060,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -11080,71 +11080,71 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11156,17 +11156,17 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -11176,7 +11176,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11188,27 +11188,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11220,49 +11220,49 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11272,39 +11272,39 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11316,27 +11316,27 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11348,27 +11348,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11380,49 +11380,49 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -11432,61 +11432,61 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -11496,61 +11496,61 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -11560,46 +11560,46 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -11614,24 +11614,24 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -11646,7 +11646,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,24 +11656,24 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -11688,61 +11688,61 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11764,81 +11764,81 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11848,29 +11848,29 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11892,27 +11892,27 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11924,17 +11924,17 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -11944,14 +11944,14 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -11966,24 +11966,24 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -11998,56 +11998,56 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -12062,71 +12062,71 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -12136,46 +12136,46 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -12190,17 +12190,17 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12212,49 +12212,49 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12271,17 +12271,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -12303,32 +12303,32 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12340,17 +12340,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12372,49 +12372,49 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,29 +12424,29 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,39 +12456,39 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12500,27 +12500,27 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12532,113 +12532,113 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12660,17 +12660,17 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12692,49 +12692,49 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -12744,61 +12744,61 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -12808,78 +12808,78 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12904,29 +12904,29 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -12936,152 +12936,152 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -13103,7 +13103,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13128,125 +13128,125 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13256,125 +13256,125 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13384,29 +13384,29 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13416,24 +13416,24 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -13455,71 +13455,71 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -13544,61 +13544,61 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,37 +13608,325 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>天安@1119</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
+      <c r="C422" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
+      <c r="D422" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F422"/>
+  <dimension ref="A1:F421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9423,22 +9423,22 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9460,17 +9460,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9492,27 +9492,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -9524,91 +9524,91 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9620,27 +9620,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9652,17 +9652,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -9684,59 +9684,59 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -9748,59 +9748,59 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -9812,22 +9812,22 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -9844,44 +9844,44 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -9896,39 +9896,39 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -9940,27 +9940,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9972,59 +9972,59 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10036,27 +10036,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10068,17 +10068,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10100,27 +10100,27 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10132,17 +10132,17 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -10152,39 +10152,39 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10196,12 +10196,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10260,49 +10260,49 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10324,27 +10324,27 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10356,17 +10356,17 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -10376,39 +10376,39 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -10420,34 +10420,34 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10462,39 +10462,39 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10516,27 +10516,27 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10548,59 +10548,59 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10612,27 +10612,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10644,27 +10644,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10676,59 +10676,59 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10740,12 +10740,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -10772,27 +10772,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -10804,27 +10804,27 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10836,49 +10836,49 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10900,59 +10900,59 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -10964,34 +10964,34 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11006,39 +11006,39 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -11060,27 +11060,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11092,49 +11092,49 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11156,27 +11156,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11188,27 +11188,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11220,17 +11220,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11252,59 +11252,59 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11316,12 +11316,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11348,27 +11348,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11412,17 +11412,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -11432,24 +11432,24 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11476,59 +11476,59 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -11540,34 +11540,34 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11582,17 +11582,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11604,49 +11604,49 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11668,27 +11668,27 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11700,49 +11700,49 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11764,27 +11764,27 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -11796,27 +11796,27 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -11828,59 +11828,59 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11892,12 +11892,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -11924,27 +11924,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11956,27 +11956,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11988,59 +11988,59 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12052,59 +12052,59 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12116,34 +12116,34 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12158,39 +12158,39 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12212,27 +12212,27 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12244,17 +12244,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12276,22 +12276,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -12303,32 +12303,32 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12340,17 +12340,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12372,17 +12372,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12404,17 +12404,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12436,59 +12436,59 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12500,17 +12500,17 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12532,27 +12532,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12564,27 +12564,27 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,39 +12616,39 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12660,27 +12660,27 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12692,27 +12692,27 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12724,27 +12724,27 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -12783,32 +12783,32 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12820,34 +12820,34 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12862,39 +12862,39 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12904,24 +12904,24 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13032,39 +13032,39 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -13108,27 +13108,27 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -13160,39 +13160,39 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13204,59 +13204,59 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -13268,34 +13268,34 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13327,32 +13327,32 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13416,24 +13416,24 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -13460,27 +13460,27 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -13492,27 +13492,27 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13524,17 +13524,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -13544,61 +13544,61 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
@@ -13620,17 +13620,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13672,24 +13672,24 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -13716,59 +13716,59 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -13780,66 +13780,66 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -13871,7 +13871,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -13895,38 +13895,6 @@
         </is>
       </c>
       <c r="F421" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C422" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F421"/>
+  <dimension ref="A1:F422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9391,32 +9391,32 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>史心怡</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9428,17 +9428,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
@@ -9460,91 +9460,91 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9556,27 +9556,27 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -9588,17 +9588,17 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -9620,98 +9620,98 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -9726,49 +9726,49 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -9780,17 +9780,17 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -9812,17 +9812,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -9832,24 +9832,24 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -9864,39 +9864,39 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -9908,27 +9908,27 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9940,59 +9940,59 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10004,27 +10004,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10036,17 +10036,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10068,27 +10068,27 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -10120,39 +10120,39 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10164,12 +10164,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10228,49 +10228,49 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10292,27 +10292,27 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10324,17 +10324,17 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -10344,39 +10344,39 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -10388,27 +10388,27 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10420,17 +10420,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10991,54 +10991,54 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -11060,27 +11060,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -11092,49 +11092,49 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11156,27 +11156,27 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11188,27 +11188,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11220,17 +11220,17 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11252,59 +11252,59 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11316,12 +11316,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -11348,27 +11348,27 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11412,17 +11412,17 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -11432,24 +11432,24 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -11476,59 +11476,59 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11540,34 +11540,34 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11582,17 +11582,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11604,49 +11604,49 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -11656,7 +11656,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
@@ -11668,27 +11668,27 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11700,49 +11700,49 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11764,27 +11764,27 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11796,27 +11796,27 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -11828,59 +11828,59 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11892,12 +11892,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -11924,27 +11924,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11956,27 +11956,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11988,59 +11988,59 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12052,59 +12052,59 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
@@ -12116,34 +12116,34 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12158,39 +12158,39 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12212,27 +12212,27 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12244,17 +12244,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12276,22 +12276,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -12303,32 +12303,32 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12340,17 +12340,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12372,17 +12372,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12404,17 +12404,17 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12436,59 +12436,59 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12500,17 +12500,17 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12532,27 +12532,27 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12564,27 +12564,27 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,39 +12616,39 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12660,27 +12660,27 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12692,27 +12692,27 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12724,27 +12724,27 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -12783,32 +12783,32 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -12820,34 +12820,34 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -12862,39 +12862,39 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12904,24 +12904,24 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12948,17 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12980,17 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13012,17 +13012,17 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13032,39 +13032,39 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13108,27 +13108,27 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -13140,17 +13140,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -13160,39 +13160,39 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13204,59 +13204,59 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
@@ -13268,34 +13268,34 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13327,32 +13327,32 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13364,17 +13364,17 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13396,17 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -13416,24 +13416,24 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13460,27 +13460,27 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -13492,27 +13492,27 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -13524,17 +13524,17 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -13544,61 +13544,61 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
@@ -13620,17 +13620,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
@@ -13652,17 +13652,17 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -13672,24 +13672,24 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -13716,59 +13716,59 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13780,66 +13780,66 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -13871,30 +13871,62 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B421" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
+      <c r="C422" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
+      <c r="D422" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F421" t="inlineStr">
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F422"/>
+  <dimension ref="A1:F425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9492,27 +9492,27 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -9524,17 +9524,17 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -9556,91 +9556,91 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9652,22 +9652,22 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -9684,27 +9684,27 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -9807,64 +9807,64 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -9876,27 +9876,27 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9908,59 +9908,59 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9972,27 +9972,27 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -10004,17 +10004,17 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10036,27 +10036,27 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10068,17 +10068,17 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -10088,39 +10088,39 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10132,12 +10132,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -10164,27 +10164,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10228,27 +10228,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
@@ -10415,54 +10415,54 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10484,27 +10484,27 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10516,59 +10516,59 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10580,27 +10580,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10612,27 +10612,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10644,27 +10644,27 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1101</t>
         </is>
       </c>
     </row>
@@ -10927,32 +10927,32 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -10964,27 +10964,27 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -10996,17 +10996,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11151,32 +11151,32 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11188,27 +11188,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11220,27 +11220,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11252,17 +11252,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11284,59 +11284,59 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11444,17 +11444,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11464,24 +11464,24 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
@@ -11508,113 +11508,113 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -11624,103 +11624,103 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
@@ -11732,17 +11732,17 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -11752,71 +11752,71 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11828,17 +11828,17 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
@@ -11848,7 +11848,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11860,49 +11860,49 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
@@ -11912,39 +11912,39 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
@@ -11956,27 +11956,27 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11988,27 +11988,27 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12020,49 +12020,49 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -12072,61 +12072,61 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -12136,93 +12136,93 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -12232,46 +12232,46 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12308,49 +12308,49 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12367,17 +12367,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -12399,32 +12399,32 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12436,17 +12436,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12468,49 +12468,49 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -12520,29 +12520,29 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -12552,39 +12552,39 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12596,27 +12596,27 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12628,113 +12628,113 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12756,17 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12788,49 +12788,49 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -12840,61 +12840,61 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -12904,14 +12904,14 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -12926,71 +12926,71 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -13000,29 +13000,29 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13064,14 +13064,14 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -13086,24 +13086,24 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13118,24 +13118,24 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13150,17 +13150,17 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
@@ -13172,34 +13172,34 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -13214,7 +13214,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
@@ -13224,14 +13224,14 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13246,34 +13246,34 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -13288,14 +13288,14 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13327,39 +13327,39 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -13374,24 +13374,24 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -13406,56 +13406,56 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13480,14 +13480,14 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -13502,24 +13502,24 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -13534,17 +13534,17 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13556,34 +13556,34 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -13598,103 +13598,103 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -13704,14 +13704,14 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13736,61 +13736,61 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
@@ -13800,78 +13800,78 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -13903,30 +13903,126 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>10:20:00</t>
         </is>
       </c>
-      <c r="C422" t="inlineStr">
+      <c r="C425" t="inlineStr">
         <is>
           <t>12:20:00</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
+      <c r="D425" t="inlineStr">
         <is>
           <t>吴子墨</t>
         </is>
       </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F422" t="inlineStr">
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F425"/>
+  <dimension ref="A1:F424"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9524,49 +9524,49 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -9576,39 +9576,39 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -9620,22 +9620,22 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -9652,59 +9652,59 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -9716,22 +9716,22 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -9748,44 +9748,44 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -9800,39 +9800,39 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -9844,27 +9844,27 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -9876,59 +9876,59 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -9940,27 +9940,27 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -9972,17 +9972,17 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -10004,27 +10004,27 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1042</t>
         </is>
       </c>
     </row>
@@ -10036,17 +10036,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -10056,39 +10056,39 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10100,12 +10100,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -10132,27 +10132,27 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10164,27 +10164,27 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
@@ -10196,59 +10196,59 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10260,27 +10260,27 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10292,17 +10292,17 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -10312,39 +10312,39 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1048</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -10356,34 +10356,34 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -10398,39 +10398,39 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -10452,27 +10452,27 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -10484,59 +10484,59 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -10548,27 +10548,27 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -10580,27 +10580,27 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -10612,27 +10612,27 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1101</t>
         </is>
       </c>
     </row>
@@ -10644,59 +10644,59 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>天安@1101</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -10708,12 +10708,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -10740,27 +10740,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -10772,27 +10772,27 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@939</t>
         </is>
       </c>
     </row>
@@ -10804,49 +10804,49 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -10868,27 +10868,27 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1008</t>
         </is>
       </c>
     </row>
@@ -10900,59 +10900,59 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -10964,34 +10964,34 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11006,39 +11006,39 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
@@ -11060,27 +11060,27 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11092,27 +11092,27 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -11124,59 +11124,59 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -11188,27 +11188,27 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
@@ -11220,27 +11220,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -11252,17 +11252,17 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -11284,59 +11284,59 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -11380,27 +11380,27 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1011</t>
         </is>
       </c>
     </row>
@@ -11412,27 +11412,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -11444,17 +11444,17 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -11464,24 +11464,24 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@947</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11508,27 +11508,27 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -11540,59 +11540,59 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@906</t>
         </is>
       </c>
     </row>
@@ -11604,34 +11604,34 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -11646,17 +11646,17 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -11668,49 +11668,49 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1030</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -11720,7 +11720,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@948</t>
         </is>
       </c>
     </row>
@@ -11732,27 +11732,27 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -11764,49 +11764,49 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -11828,27 +11828,27 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@956</t>
         </is>
       </c>
     </row>
@@ -11860,27 +11860,27 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1126</t>
         </is>
       </c>
     </row>
@@ -11892,59 +11892,59 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1058</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -11956,12 +11956,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -11988,27 +11988,27 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12020,27 +12020,27 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12052,59 +12052,59 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12116,27 +12116,27 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>国金@2117</t>
         </is>
       </c>
     </row>
@@ -12148,59 +12148,59 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@937</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12212,34 +12212,34 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -12254,39 +12254,39 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -12308,27 +12308,27 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12340,17 +12340,17 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -12360,7 +12360,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12372,22 +12372,22 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -12399,32 +12399,32 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12436,17 +12436,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1010</t>
         </is>
       </c>
     </row>
@@ -12468,17 +12468,17 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -12500,17 +12500,17 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>网络授课</t>
         </is>
       </c>
     </row>
@@ -12532,59 +12532,59 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12596,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -12628,27 +12628,27 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12660,27 +12660,27 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12692,17 +12692,17 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -12712,39 +12712,39 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>管子栋</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1068</t>
         </is>
       </c>
     </row>
@@ -12756,27 +12756,27 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>管子栋</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -12788,27 +12788,27 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
     </row>
@@ -12820,27 +12820,27 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1029</t>
         </is>
       </c>
     </row>
@@ -12852,12 +12852,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -12879,32 +12879,32 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -12916,34 +12916,34 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -12958,39 +12958,39 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -13000,24 +13000,24 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1130</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13044,17 +13044,17 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13076,17 +13076,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -13096,7 +13096,7 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
@@ -13108,17 +13108,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -13128,39 +13128,39 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1021</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>天安@1021</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -13204,27 +13204,27 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13236,17 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
@@ -13256,39 +13256,39 @@
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
@@ -13300,59 +13300,59 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@903</t>
         </is>
       </c>
     </row>
@@ -13364,34 +13364,34 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>黄思涵</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@949</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -13423,32 +13423,32 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>黄思涵</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>天安@949</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
@@ -13460,17 +13460,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13492,17 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -13512,24 +13512,24 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -13544,7 +13544,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1039</t>
         </is>
       </c>
     </row>
@@ -13556,27 +13556,27 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>天安@1039</t>
+          <t>国金@2108</t>
         </is>
       </c>
     </row>
@@ -13588,27 +13588,27 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
@@ -13620,17 +13620,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -13640,61 +13640,61 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@904</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1031</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>盛晨轩</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>天安@1119</t>
         </is>
       </c>
     </row>
@@ -13716,17 +13716,17 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>天安@1119</t>
+          <t>天安@1027</t>
         </is>
       </c>
     </row>
@@ -13748,17 +13748,17 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -13768,24 +13768,24 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@1007</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -13812,59 +13812,59 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1028</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
@@ -13876,66 +13876,66 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1032</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@1025</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -13967,7 +13967,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -13991,38 +13991,6 @@
         </is>
       </c>
       <c r="F424" t="inlineStr">
-        <is>
-          <t>天安@1025</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>2026-06-20</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>10:20:00</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>12:20:00</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>吴子墨</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>A-LEVEL数学</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
         <is>
           <t>天安@1025</t>
         </is>

--- a/彼岸课程.xlsx
+++ b/彼岸课程.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,133 +473,133 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1065</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>AP强化班（全程班）</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@904</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1065</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>AP强化班（全程班）</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1016</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -641,74 +641,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>天安@1037</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -718,14 +718,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -740,59 +740,59 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@939</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -802,197 +802,197 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>天安@1042</t>
+          <t>天安@947</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享（旧）-AP1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1032</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>AP考前冲刺班（大师班）</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>天安@1026</t>
+          <t>天安@1065</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>AP强化班（全程班）</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1007</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1019,116 +1019,116 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@939</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>袁芷澜</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>天安@1031</t>
+          <t>太阳城@416</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@947</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1138,39 +1138,39 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>李逸舟</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>天安@1129</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1180,182 +1180,182 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>郑煦翔</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>天安@1048</t>
+          <t>天安@939</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 B计划VIP纯享（旧）-AP1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>周宏胤</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>仙林高科校区 仙林高科校区VIP806教室</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@904</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>李逸舟</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>天安@1013</t>
+          <t>天安@1032</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1370,34 +1370,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1064</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP强化班（全程班）</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1412,17 +1412,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>李逸舟</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>A-LEVEL计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>天安@1008</t>
+          <t>天安@1039</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1432,14 +1432,14 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>翟沅琪</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@1121</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1481,74 +1481,74 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1016</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>薛天泽</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1558,14 +1558,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@906</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1622,34 +1622,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>天安@1025</t>
+          <t>天安@1121</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1664,17 +1664,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>天安@1101</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1684,98 +1684,98 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@937</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>AP考前冲刺班（大师班）</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>程子萌</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@904</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1817,175 +1817,175 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>天安@1011</t>
+          <t>天安@1068</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>天安@939</t>
+          <t>天安@1032</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1025</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1039</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享（旧）-AP1对1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2000,34 +2000,34 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1058</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GCSE/IGCSE1对1</t>
+          <t>AP考前冲刺班（大师班）</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2042,34 +2042,34 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1127</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1022</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>天安@1024</t>
+          <t>天安@909</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2153,91 +2153,91 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>天安@1029</t>
+          <t>天安@904</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>史心怡</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1125</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2252,34 +2252,34 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>天安@1130</t>
+          <t>天安@904</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@937</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2321,22 +2321,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2363,91 +2363,91 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>张可馨</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1048</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>天安@1068</t>
+          <t>天安@1058</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP考前冲刺班（大师班）</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2462,133 +2462,133 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>天安@1032</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>天安@1027</t>
+          <t>天安@904</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>天安@1028</t>
+          <t>天安@947</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>许宸铭</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2598,39 +2598,39 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1068</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>AP考前冲刺班（大师班）</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>盛晨轩</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1068</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2657,74 +2657,74 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>李佳澄</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>计算机</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@937</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>GCSE/IGCSE1对1</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>天安@1020</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2734,34 +2734,34 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2776,24 +2776,24 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@947</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2825,32 +2825,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>国金@2108</t>
+          <t>天安@1121</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2860,81 +2860,81 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1130</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GCSE/IGCSE1对1</t>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1037</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2944,81 +2944,81 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>天安@906</t>
+          <t>天安@1010</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>陈博扬</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1032</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3028,29 +3028,29 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>杨涵予</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>天安@1007</t>
+          <t>天安@1126</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3077,7 +3077,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3092,133 +3092,133 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>天安@1030</t>
+          <t>天安@1042</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 B计划VIP纯享（旧）-AP1对1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>班课</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP计算机</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>天安@948</t>
+          <t>天安@1058</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+          <t>AP考前冲刺班（大师班）</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>全科</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>天安@947</t>
+          <t>天安@1026</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>陆奕心</t>
+          <t>王振宁</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3228,12 +3228,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>天安@1010</t>
+          <t>天安@1068</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3245,74 +3245,74 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>金明珺</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@937</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>陈博扬</t>
+          <t>张可馨</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>天安@956</t>
+          <t>天安@1031</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3322,14 +3322,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3344,34 +3344,34 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>吴子墨</t>
+          <t>徐梓原</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>天安@1126</t>
+          <t>天安@1121</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3386,34 +3386,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>陈佳禾</t>
+          <t>李逸舟</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AP统计学</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>天安@1041</t>
+          <t>天安@1129</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>统计学</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>班课</t>
+          <t>郑煦翔</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3438,108 +3438,108 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>天安@1058</t>
+          <t>天安@1048</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>AP考前冲刺班（大师班）</t>
+          <t>高中英联邦计划卡 B计划VIP纯享（旧）-AP1对1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>司凝</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP微积分</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@903</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>微积分BC</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>王振宁</t>
+          <t>陈佳禾</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>A-LEVEL数学</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>网络授课</t>
+          <t>天安@1007</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+          <t>AP1对1</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>高等数学</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3554,49 +3554,49 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>李逸舟</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1013</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:50:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>15:50:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>杨涵予</t>
+          <t>吴子墨</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>天安@904</t>
+          <t>天安@1030</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3623,158 +3623,158 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>13:50:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>15:50:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>徐梓原</t>
+          <t>李逸舟</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>A-LEVEL计算机</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>天安@1121</t>
+          <t>天安@1008</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>计算机科学</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:10:00</t>
+          <t>10:20:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>12:20:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>许宸铭</t>
+          <t>金明珺</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AP计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>国金@2117</t>
+          <t>天安@1130</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AP1对1</t>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:10:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>李佳澄</t>
+          <t>陆奕心</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>计算机</t>
+          <t>A-LEVEL数学</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>天安@937</t>
+          <t>天安@1010</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>GCSE/IGCSE1对1</t>
+          <t>A-LEVEL1对1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>计算机科学</t>
+          <t>高等数学</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>10:20:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>12:20:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>司凝</t>
+          <t>薛天泽</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AP微积分</t>
+          <t>AP统计学</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>天安@903</t>
+          <t>天安@1028</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3784,49 +3784,4627 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>微积分BC</t>
+          <t>统计学</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>天安@1025</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>张可馨</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>天安@1101</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>班课</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>天安@1058</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>AP考前冲刺班（大师班）</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>全科</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>天安@1011</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>杨涵予</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>天安@939</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>天安@1121</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>李佳澄</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>GCSE/IGCSE1对1</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>天安@906</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>陈佳禾</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>天安@1024</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>天安@1029</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>天安@1121</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>天安@1130</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>陈佳禾</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>天安@1010</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>张可馨</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>天安@1068</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>天安@1032</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>杨涵予</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>班课</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>天安@1058</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>AP考前冲刺班（大师班）</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>全科</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>天安@1020</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>天安@1121</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>国金@2108</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>李佳澄</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>天安@937</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>GCSE/IGCSE1对1</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>天安@1121</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>天安@906</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>陈佳禾</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>天安@1030</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>天安@948</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>天安@947</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>天安@1010</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>天安@956</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>天安@1126</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>陈佳禾</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>天安@1041</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>班课</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>天安@1058</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>AP考前冲刺班（大师班）</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>全科</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>杨涵予</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>徐梓原</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>天安@1121</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>国金@2117</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>李佳澄</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>计算机</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>天安@937</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>GCSE/IGCSE1对1</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
         <is>
           <t>13:50:00</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>15:50:00</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>陈佳禾</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>AP统计学</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>天安@1007</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>AP1对1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>杨涵予</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>天安@1010</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>陈佳禾</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>天安@1010</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>张可馨</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>天安@1010</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>王振宁</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>网络授课</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 A计划VIP纯享-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>许宸铭</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>国金@2108</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>天安@1029</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>天安@1029</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>天安@903</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>陈佳禾</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AP统计学</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>统计学</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>盛晨轩</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>天安@1031</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>天安@1130</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>08:00:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>金明珺</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>高中英联邦计划卡 VIP-A计划 78000-A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>吴子墨</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>天安@1027</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>13:50:00</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>15:50:00</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>陆奕心</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>天安@1007</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>高等数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>杨涵予</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>A-LEVEL数学</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>天安@1021</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>A-LEVEL1对1</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>基础数学</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>10:20:00</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>12:20:00</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>黄思涵</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AP计算机</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>天安@948</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>计算机科学</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>16:10:00</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>18:10:00</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>陈博扬</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>天安@1028</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>司凝</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AP微积分</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>天安@904</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>AP1对1</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>微积分BC</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      <